--- a/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\깃의 템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3E0E9D-0EAD-422C-A3C8-3A6FF1840880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>
@@ -382,20 +382,20 @@
     <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -683,209 +683,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -893,11 +898,6 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[내가시스템]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\깃의 템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3E0E9D-0EAD-422C-A3C8-3A6FF1840880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E9E567-3E21-4432-B3EF-3AFB012346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30495" yWindow="1245" windowWidth="24705" windowHeight="13470" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>
     <sheet name="주간실적입력" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -382,34 +382,34 @@
     <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -683,214 +683,209 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
     </row>
     <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -898,6 +893,11 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -918,31 +918,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -989,7 +989,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11">
-        <v>11119</v>
+        <v>11054</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1081,14 +1081,14 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
       <c r="D12" s="3">
         <f>SUM(D5:D11)</f>
-        <v>13995</v>
+        <v>13930</v>
       </c>
       <c r="E12" s="3">
         <f>SUM(E5:E11)</f>
@@ -1096,13 +1096,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
